--- a/教員見回り配布用.xlsx
+++ b/教員見回り配布用.xlsx
@@ -21,11 +21,11 @@
     <sheet name="7-30木_教員1" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="7-30木_教員2" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="7-30木_教員3" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="7-31金_教員1" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="7-31金_教員2" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="7-31金_教員3" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="7-31金_教員4" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="7-31金_教員5" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="7-30木_教員4" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="7-31金_教員1" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="7-31金_教員2" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="7-31金_教員3" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="7-31金_教員4" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="8-24月_教員1" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="8-24月_教員2" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="8-24月_教員3" sheetId="22" state="visible" r:id="rId22"/>
@@ -130,7 +130,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -189,11 +189,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0076448A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
@@ -208,7 +203,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -356,25 +351,11 @@
         <color rgb="00D68910"/>
       </bottom>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="0076448A"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="0076448A"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="0076448A"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -424,13 +405,10 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -460,11 +438,11 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -484,12 +462,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1222,22 +1194,22 @@
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>江南市立古知野東保育園 → 江南市立小鹿保育園 → リスパック株式会社 真空成形工場</t>
+          <t>江南市立藤里保育園</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>江南市高屋町大師７２番地 ／ 江南市小杁町長者毛東1 ／ 愛知県犬山市羽黒宮浦1番地</t>
+          <t>江南市藤が丘7丁目1-16</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>1-5-3　1-5-31　1-5-36　2-2-8　1-5-6　2-1-27　2-1-28　2-3-11　2-3-17</t>
+          <t>2-4-7</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>14.9km</t>
+          <t>7.2km</t>
         </is>
       </c>
     </row>
@@ -1278,167 +1250,167 @@
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>江南市立藤里保育園 → ＮＸキャッシュ・ロジスティクス株式会社　中部支店</t>
+          <t>江南市立古知野東保育園 → 江南市立小鹿保育園 → リスパック株式会社 真空成形工場</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>江南市藤が丘7丁目1-16 ／ 愛知県名古屋市中村区並木1-81-1</t>
+          <t>江南市高屋町大師７２番地 ／ 江南市小杁町長者毛東1 ／ 愛知県犬山市羽黒宮浦1番地</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>2-4-7　2-2-9　2-2-11　2-2-15　2-4-12</t>
+          <t>1-5-3　1-5-31　1-5-36　2-2-8　1-5-6　2-1-27　2-1-28　2-3-11　2-3-17</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>45.9km</t>
+          <t>14.9km</t>
         </is>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>7/31(金)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>教員 1</t>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>教員 4</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>江南市立布袋北保育園 → 江南市立古知野南保育園 → 九品寺幼稚園</t>
+          <t>ＮＸキャッシュ・ロジスティクス株式会社　中部支店</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>江南市安良町八王子137 ／ 江南市古知野町塔塚160 ／ 一宮市真清田2-14-7</t>
+          <t>愛知県名古屋市中村区並木1-81-1</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>1-5-28　1-5-23　2-1-17　1-5-5</t>
+          <t>2-2-9　2-2-11　2-2-15　2-4-12</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>18.0km</t>
+          <t>40.6km</t>
         </is>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>教員 2</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>7/31(金)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>教員 1</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>東罐興業株式会社　小牧工場</t>
+          <t>江南市立布袋北保育園 → 江南市立古知野南保育園 → 九品寺幼稚園</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>愛知県小牧市東田中2118</t>
+          <t>江南市安良町八王子137 ／ 江南市古知野町塔塚160 ／ 一宮市真清田2-14-7</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>1-5-34</t>
+          <t>1-5-28　1-5-23　2-1-17　1-5-5</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>12.8km</t>
+          <t>18.0km</t>
         </is>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>教員 3</t>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>教員 2</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>グンゼ江南工場 → 江南市立宮田東保育園</t>
+          <t>東罐興業株式会社　小牧工場 → 東名化学工業株式会社　小牧工場</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>愛知県江南市村久野町鳥附１番地 ／ 江南市宮田神明町栄174</t>
+          <t>愛知県小牧市東田中2118 ／ 小牧市大草檀之上5410</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25</t>
+          <t>1-5-34　2-3-8　2-3-13</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>8.3km</t>
+          <t>22.3km</t>
         </is>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>教員 4</t>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>教員 3</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>福玉ロジスティクス株式会社　大口センター → 株式会社メイコン　本社 → 東名化学工業株式会社　小牧工場</t>
+          <t>江南市立古知野東保育園 → グンゼ江南工場 → 江南市立宮田東保育園</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>集合場所：丹羽郡大口町御供所1-65　就業体験場所：丹羽郡大口町御供所3丁目122番地 ／ 本社（愛知県小牧市大字三ツ渕950番地） ／ 小牧市大草檀之上5410</t>
+          <t>江南市高屋町大師７２番地 ／ 愛知県江南市村久野町鳥附１番地 ／ 江南市宮田神明町栄174</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>2-4-18　2-4-25　2-1-14　2-2-6　2-4-24　2-3-8　2-3-13</t>
+          <t>2-4-22　1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>26.1km</t>
+          <t>8.4km</t>
         </is>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>教員 5</t>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>教員 4</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>江南市立古知野東保育園</t>
+          <t>福玉ロジスティクス株式会社　大口センター → 株式会社メイコン　本社</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>江南市高屋町大師７２番地</t>
+          <t>集合場所：丹羽郡大口町御供所1-65　就業体験場所：丹羽郡大口町御供所3丁目122番地 ／ 本社（愛知県小牧市大字三ツ渕950番地）</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>2-4-22</t>
+          <t>2-4-18　2-4-25　2-1-14　2-2-6　2-4-24</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>3.2km</t>
+          <t>9.2km</t>
         </is>
       </c>
     </row>
@@ -1833,16 +1805,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A13:A16"/>
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="A17:A20"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1871,51 +1843,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>教員 3　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C11</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="36" t="n">
+      <c r="A6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>株式会社綿半ホームエイド江南店</t>
         </is>
@@ -1925,7 +1897,7 @@
           <t>江南市上奈良町緑13</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 2.9km</t>
@@ -1933,17 +1905,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-21　2-2-4</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立藤里保育園</t>
         </is>
@@ -1953,7 +1925,7 @@
           <t>江南市藤が丘7丁目1-16</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 2.2km</t>
@@ -1961,38 +1933,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-2-20</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>合計　2社 / 3名 / 計8.6km</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2040,51 +2012,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>教員 4　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C12</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>株式会社青山製作所　大口工場</t>
         </is>
@@ -2094,7 +2066,7 @@
           <t>愛知県丹羽郡大口町高橋一丁目8番地</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 1.1km</t>
@@ -2102,17 +2074,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-2-14　2-4-21</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>キムラユニティー株式会社　犬山工場</t>
         </is>
@@ -2122,7 +2094,7 @@
           <t>愛知県犬山市字舟田10番地</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 4.4km</t>
@@ -2130,38 +2102,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-1　2-1-19　2-4-14</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>合計　2社 / 5名 / 計10.3km</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2192,7 +2164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2209,176 +2181,114 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>教員 1　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C13</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>江南市立古知野東保育園</t>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>江南市立藤里保育園</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>江南市高屋町大師７２番地</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+          <t>江南市藤が丘7丁目1-16</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
-1.6km</t>
+3.6km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>担当生徒: 1-5-3　1-5-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>江南市立小鹿保育園</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>江南市小杁町長者毛東1</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>前より
-2.1km</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>担当生徒: 1-5-36　2-2-8</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>リスパック株式会社 真空成形工場</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>愛知県犬山市羽黒宮浦1番地</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>前より
-6.3km</t>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>担当生徒: 2-4-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>合計　1社 / 1名 / 計7.2km</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>担当生徒: 1-5-6　2-1-27　2-1-28　2-3-11　2-3-17</t>
-        </is>
-      </c>
+      <c r="A11" s="31" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>合計　3社 / 9名 / 計14.9km</t>
-        </is>
-      </c>
-      <c r="D12" s="30" t="n"/>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>備考・メモ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A12" s="31" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="31" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="12">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
@@ -2409,51 +2319,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>教員 2　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C14</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>江南市立古知野中保育園</t>
         </is>
@@ -2463,7 +2373,7 @@
           <t>江南市古知野町熱田203</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 2.0km</t>
@@ -2471,17 +2381,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-18　1-5-39　2-4-3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立古知野西保育園</t>
         </is>
@@ -2491,7 +2401,7 @@
           <t>江南市東野町郷前48</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 1.9km</t>
@@ -2499,17 +2409,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-2　1-5-32</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>ガレ・ドゥ・ワタナベ</t>
         </is>
@@ -2519,7 +2429,7 @@
           <t>江南市小折町八反畑8</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
 3.3km</t>
@@ -2527,38 +2437,38 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-33　1-5-38</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>合計　3社 / 7名 / 計9.7km</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -2592,175 +2502,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>見回り担当シート　7/30(木)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
-        <is>
-          <t>教員 3　担当　　※このシートを持参してください</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>氏名</t>
-        </is>
-      </c>
-      <c r="B3" s="20">
-        <f>'全日程一覧'!C15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="6" customHeight="1"/>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>企業名　／　担当生徒</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>住　所　（訪問先）</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>距離</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>江南市立藤里保育園</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>江南市藤が丘7丁目1-16</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>学校から
-3.6km</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>担当生徒: 2-4-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>ＮＸキャッシュ・ロジスティクス株式会社　中部支店</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>愛知県名古屋市中村区並木1-81-1</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>前より
-22.0km</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>担当生徒: 2-2-9　2-2-11　2-2-15　2-4-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>合計　2社 / 5名 / 計45.9km</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="n"/>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>備考・メモ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2773,161 +2514,161 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>見回り担当シート　7/31(金)</t>
+          <t>見回り担当シート　7/30(木)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>教員 1　担当　　※このシートを持参してください</t>
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>教員 3　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
-        <f>'全日程一覧'!C16</f>
+      <c r="B3" s="19">
+        <f>'全日程一覧'!C15</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>江南市立布袋北保育園</t>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>江南市立古知野東保育園</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>江南市安良町八王子137</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+          <t>江南市高屋町大師７２番地</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
-1.3km</t>
+1.6km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>担当生徒: 1-5-28</t>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>担当生徒: 1-5-3　1-5-31</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>江南市立古知野南保育園</t>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>江南市立小鹿保育園</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>江南市古知野町塔塚160</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
+          <t>江南市小杁町長者毛東1</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
-1.8km</t>
+2.1km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>担当生徒: 1-5-23　2-1-17</t>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>担当生徒: 1-5-36　2-2-8</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>九品寺幼稚園</t>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>リスパック株式会社 真空成形工場</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>一宮市真清田2-14-7</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
+          <t>愛知県犬山市羽黒宮浦1番地</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
-6.5km</t>
+6.3km</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>担当生徒: 1-5-5</t>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>担当生徒: 1-5-6　2-1-27　2-1-28　2-3-11　2-3-17</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>合計　3社 / 4名 / 計18.0km</t>
-        </is>
-      </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>合計　3社 / 9名 / 計14.9km</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -2955,7 +2696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2973,105 +2714,105 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>見回り担当シート　7/31(金)</t>
+          <t>見回り担当シート　7/30(木)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
-        <is>
-          <t>教員 2　担当　　※このシートを持参してください</t>
+      <c r="A2" s="36" t="inlineStr">
+        <is>
+          <t>教員 4　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
-        <f>'全日程一覧'!C17</f>
+      <c r="B3" s="19">
+        <f>'全日程一覧'!C16</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>東罐興業株式会社　小牧工場</t>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>ＮＸキャッシュ・ロジスティクス株式会社　中部支店</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>愛知県小牧市東田中2118</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+          <t>愛知県名古屋市中村区並木1-81-1</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
-6.4km</t>
+20.3km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>担当生徒: 1-5-34</t>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>担当生徒: 2-2-9　2-2-11　2-2-15　2-4-12</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>合計　1社 / 1名 / 計12.8km</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="n"/>
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>合計　1社 / 4名 / 計40.6km</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="32" t="inlineStr"/>
+      <c r="A11" s="31" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="32" t="inlineStr"/>
+      <c r="A12" s="31" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3086,6 +2827,206 @@
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>見回り担当シート　7/31(金)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>教員 1　担当　　※このシートを持参してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="B3" s="19">
+        <f>'全日程一覧'!C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="6" customHeight="1"/>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>企業名　／　担当生徒</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>住　所　（訪問先）</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>距離</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>江南市立布袋北保育園</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>江南市安良町八王子137</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>学校から
+1.3km</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>担当生徒: 1-5-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>江南市立古知野南保育園</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>江南市古知野町塔塚160</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>前より
+1.8km</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>担当生徒: 1-5-23　2-1-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>九品寺幼稚園</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>一宮市真清田2-14-7</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>前より
+6.5km</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>担当生徒: 1-5-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>合計　3社 / 4名 / 計18.0km</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="n"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>備考・メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="31" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="31" t="inlineStr"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="31" t="inlineStr"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="31" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
@@ -3116,128 +3057,128 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
-        <is>
-          <t>教員 3　担当　　※このシートを持参してください</t>
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>教員 2　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C18</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="36" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>グンゼ江南工場</t>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>東罐興業株式会社　小牧工場</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>愛知県江南市村久野町鳥附１番地</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+          <t>愛知県小牧市東田中2118</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
-2.8km</t>
+6.4km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>担当生徒: 1-5-24　2-1-29　2-1-32　2-3-12　2-3-15</t>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>担当生徒: 1-5-34</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>江南市立宮田東保育園</t>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>東名化学工業株式会社　小牧工場</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>江南市宮田神明町栄174</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
+          <t>小牧市大草檀之上5410</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
-1.3km</t>
+5.1km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>担当生徒: 1-5-1　1-5-25</t>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>担当生徒: 2-3-8　2-3-13</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>合計　2社 / 7名 / 計8.3km</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>合計　2社 / 3名 / 計22.3km</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3285,156 +3226,156 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="37" t="inlineStr">
-        <is>
-          <t>教員 4　担当　　※このシートを持参してください</t>
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>教員 3　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C19</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>福玉ロジスティクス株式会社　大口センター</t>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>江南市立古知野東保育園</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>集合場所：丹羽郡大口町御供所1-65　就業体験場所：丹羽郡大口町御供所3丁目122番地</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+          <t>江南市高屋町大師７２番地</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
-2.1km</t>
+1.6km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>担当生徒: 2-4-18　2-4-25</t>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>担当生徒: 2-4-22</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>株式会社メイコン　本社</t>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>グンゼ江南工場</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>本社（愛知県小牧市大字三ツ渕950番地）</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
+          <t>愛知県江南市村久野町鳥附１番地</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
-2.5km</t>
+1.3km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>担当生徒: 2-1-14　2-2-6　2-4-24</t>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>担当生徒: 1-5-24　2-1-29　2-1-32　2-3-12　2-3-15</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>東名化学工業株式会社　小牧工場</t>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>江南市立宮田東保育園</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>小牧市大草檀之上5410</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
+          <t>江南市宮田神明町栄174</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
-10.7km</t>
+1.3km</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>担当生徒: 2-3-8　2-3-13</t>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>担当生徒: 1-5-1　1-5-25</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>合計　3社 / 7名 / 計26.1km</t>
-        </is>
-      </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>合計　3社 / 8名 / 計8.4km</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3468,7 +3409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3485,111 +3426,142 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>教員 5　担当　　※このシートを持参してください</t>
+      <c r="A2" s="36" t="inlineStr">
+        <is>
+          <t>教員 4　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C20</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="40" t="n">
+      <c r="A6" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>江南市立古知野東保育園</t>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>福玉ロジスティクス株式会社　大口センター</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>江南市高屋町大師７２番地</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+          <t>集合場所：丹羽郡大口町御供所1-65　就業体験場所：丹羽郡大口町御供所3丁目122番地</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
-1.6km</t>
+2.1km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>担当生徒: 2-4-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>合計　1社 / 1名 / 計3.2km</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="n"/>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>担当生徒: 2-4-18　2-4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>株式会社メイコン　本社</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>本社（愛知県小牧市大字三ツ渕950番地）</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>前より
+2.5km</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>担当生徒: 2-1-14　2-2-6　2-4-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>合計　2社 / 5名 / 計9.2km</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="32" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="32" t="inlineStr"/>
-    </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="31" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="15">
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A13:D13"/>
@@ -3623,51 +3595,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>教員 1　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C3</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>きもの館なかね</t>
         </is>
@@ -3677,7 +3649,7 @@
           <t>愛知県江南市古知野町本郷３４</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 1.8km</t>
@@ -3685,17 +3657,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-9　1-5-10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立宮田南保育園</t>
         </is>
@@ -3705,7 +3677,7 @@
           <t>江南市前飛保町西町　2</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 1.9km</t>
@@ -3713,17 +3685,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-26</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>株式会社扶桑守口食品</t>
         </is>
@@ -3733,7 +3705,7 @@
           <t>愛知県丹羽郡扶桑町大字山那字屋敷地757</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
 5.8km</t>
@@ -3741,38 +3713,38 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-30　1-5-40</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>合計　3社 / 5名 / 計14.1km</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3823,51 +3795,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>教員 1　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C21</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>美容室ISA</t>
         </is>
@@ -3877,7 +3849,7 @@
           <t>丹羽郡大口町丸2-36 メガドンキユニー大口店　1F</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 1.4km</t>
@@ -3885,17 +3857,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-33　2-3-18</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立古知野東保育園</t>
         </is>
@@ -3905,7 +3877,7 @@
           <t>江南市高屋町大師７２番地</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 2.8km</t>
@@ -3913,17 +3885,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-4-5　2-4-26</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>江南市立小鹿保育園</t>
         </is>
@@ -3933,7 +3905,7 @@
           <t>江南市小杁町長者毛東1</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
 2.1km</t>
@@ -3941,38 +3913,38 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-3-1　2-4-27</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>合計　3社 / 6名 / 計9.9km</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4023,51 +3995,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>教員 2　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C22</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>きもの館なかね</t>
         </is>
@@ -4077,7 +4049,7 @@
           <t>愛知県江南市古知野町本郷３４</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 1.8km</t>
@@ -4085,17 +4057,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-4-2　2-4-4</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立門弟山保育園</t>
         </is>
@@ -4105,7 +4077,7 @@
           <t>江南市村久野町門弟山271</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 1.3km</t>
@@ -4113,17 +4085,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-3　2-3-3</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>江南市立古知野西保育園</t>
         </is>
@@ -4133,7 +4105,7 @@
           <t>江南市東野町郷前48</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
 1.9km</t>
@@ -4141,38 +4113,38 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-4-8</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>合計　3社 / 5名 / 計8.5km</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4223,51 +4195,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>教員 3　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C23</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="36" t="n">
+      <c r="A6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>福玉米粒麦株式会社</t>
         </is>
@@ -4277,7 +4249,7 @@
           <t>愛知県江南市南山町西31</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 2.5km</t>
@@ -4285,17 +4257,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-22　2-2-1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立布袋保育園</t>
         </is>
@@ -4305,7 +4277,7 @@
           <t>江南市布袋下山町南70</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 0.4km</t>
@@ -4313,38 +4285,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-2-12</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>合計　2社 / 3名 / 計5.7km</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -4392,51 +4364,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>教員 1　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C24</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>株式会社青山製作所　大口工場</t>
         </is>
@@ -4446,7 +4418,7 @@
           <t>愛知県丹羽郡大口町高橋一丁目8番地</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 1.1km</t>
@@ -4454,17 +4426,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-3-10　2-4-13</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>株式会社東海理化電機製作所</t>
         </is>
@@ -4474,7 +4446,7 @@
           <t>愛知県丹羽郡大口町豊田三丁目260番地</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 1.9km</t>
@@ -4482,17 +4454,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-34　2-1-35　2-4-29</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>江南郵便局</t>
         </is>
@@ -4502,7 +4474,7 @@
           <t>江南市赤童子町良原143-1</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
 3.6km</t>
@@ -4510,38 +4482,38 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-7　2-2-3　2-2-5</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>合計　3社 / 8名 / 計8.7km</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4592,51 +4564,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>教員 2　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C25</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>江南市立宮田南保育園</t>
         </is>
@@ -4646,7 +4618,7 @@
           <t>江南市前飛保町西町　2</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 3.8km</t>
@@ -4654,17 +4626,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-18　2-4-6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立宮田東保育園</t>
         </is>
@@ -4674,7 +4646,7 @@
           <t>江南市宮田神明町栄174</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 1.7km</t>
@@ -4682,38 +4654,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>合計　2社 / 3名 / 計9.6km</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -4761,51 +4733,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>教員 3　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C26</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="36" t="n">
+      <c r="A6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>株式会社愛知イエローハット　一宮店</t>
         </is>
@@ -4815,7 +4787,7 @@
           <t>一宮市緑４－３ー１３</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 7.2km</t>
@@ -4823,17 +4795,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-2-2　2-2-18</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>TJ天気予報 7mm 北名古屋店</t>
         </is>
@@ -4843,7 +4815,7 @@
           <t>北名古屋市鹿田才海82番2</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 8.9km</t>
@@ -4851,38 +4823,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-10　2-1-31</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>合計　2社 / 4名 / 計27.0km</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -4930,51 +4902,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>教員 1　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C27</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>株式会社綿半ホームエイド江南店</t>
         </is>
@@ -4984,7 +4956,7 @@
           <t>江南市上奈良町緑13</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 2.9km</t>
@@ -4992,17 +4964,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-9　2-1-20</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立布袋東保育園</t>
         </is>
@@ -5012,7 +4984,7 @@
           <t>江南市小折町八反畑１４７</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 2.9km</t>
@@ -5020,38 +4992,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-24　2-2-10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>合計　2社 / 4名 / 計8.6km</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -5099,51 +5071,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>教員 2　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C28</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>株式会社愛知イエローハット　一宮店</t>
         </is>
@@ -5153,7 +5125,7 @@
           <t>一宮市緑４－３ー１３</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 7.2km</t>
@@ -5161,17 +5133,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-2-7　2-3-16</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>サロンド榮</t>
         </is>
@@ -5181,7 +5153,7 @@
           <t>一宮市浅野西大土106</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 0.7km</t>
@@ -5189,17 +5161,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-26</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>九品寺幼稚園</t>
         </is>
@@ -5209,7 +5181,7 @@
           <t>一宮市真清田2-14-7</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
 2.8km</t>
@@ -5217,38 +5189,38 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-8　2-4-9</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>合計　3社 / 5名 / 計19.1km</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -5299,51 +5271,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>教員 3　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C29</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="36" t="n">
+      <c r="A6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>株式会社デンケン</t>
         </is>
@@ -5353,7 +5325,7 @@
           <t>愛知県犬山市大字羽黒字馬道7番地1</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 7.8km</t>
@@ -5361,38 +5333,38 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-25　2-4-28</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>合計　1社 / 2名 / 計15.5km</t>
         </is>
       </c>
-      <c r="D8" s="30" t="n"/>
+      <c r="D8" s="29" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="32" t="inlineStr"/>
+      <c r="A11" s="31" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="32" t="inlineStr"/>
+      <c r="A12" s="31" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -5437,51 +5409,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>教員 4　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C30</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>アメーテールアーム</t>
         </is>
@@ -5491,7 +5463,7 @@
           <t>愛知県小牧市市之久田1-73-1</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 7.1km</t>
@@ -5499,17 +5471,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-12　2-4-10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>アイカテック建材株式会社名古屋工場</t>
         </is>
@@ -5519,7 +5491,7 @@
           <t>愛知県海部郡大治町大字西條字西之川２５</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 13.9km</t>
@@ -5527,38 +5499,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-3-5　2-3-19　2-4-17</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>合計　2社 / 5名 / 計38.7km</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -5606,51 +5578,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>教員 2　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C4</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>株式会社青山製作所　大口工場</t>
         </is>
@@ -5660,7 +5632,7 @@
           <t>愛知県丹羽郡大口町高橋一丁目8番地</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 1.1km</t>
@@ -5668,17 +5640,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-17　2-1-11</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>大口屋木賀工場</t>
         </is>
@@ -5688,7 +5660,7 @@
           <t>江南市木賀町定和244-1 その他</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 2.4km</t>
@@ -5696,38 +5668,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-20　1-5-21</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>合計　2社 / 4名 / 計5.8km</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -5775,51 +5747,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>教員 1　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C31</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>株式会社林商店</t>
         </is>
@@ -5829,7 +5801,7 @@
           <t>愛知県江南市野白町東千丸88</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 1.7km</t>
@@ -5837,17 +5809,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-4-15　2-4-19</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立宮田保育園</t>
         </is>
@@ -5857,7 +5829,7 @@
           <t>江南市飛保町新開23</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 1.1km</t>
@@ -5865,17 +5837,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-30　2-2-19</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>株式会社デンケン</t>
         </is>
@@ -5885,7 +5857,7 @@
           <t>愛知県犬山市大字羽黒字馬道7番地1</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
 9.9km</t>
@@ -5893,38 +5865,38 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-3-14　2-4-16</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>合計　3社 / 6名 / 計20.5km</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -5975,51 +5947,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>教員 2　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C32</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>江南市立布袋東保育園</t>
         </is>
@@ -6029,7 +6001,7 @@
           <t>江南市小折町八反畑１４７</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 2.9km</t>
@@ -6037,17 +6009,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-3-6　2-4-23</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>株式会社愛知イエローハット　一宮店</t>
         </is>
@@ -6057,7 +6029,7 @@
           <t>一宮市緑４－３ー１３</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 5.0km</t>
@@ -6065,17 +6037,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-2-16　2-3-7</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>FUSION</t>
         </is>
@@ -6085,7 +6057,7 @@
           <t>一宮市大江2-9-19</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
 1.8km</t>
@@ -6093,38 +6065,38 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-2-17</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>合計　3社 / 5名 / 計18.3km</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -6175,51 +6147,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>教員 1　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C33</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>江南市立布袋北保育園</t>
         </is>
@@ -6229,7 +6201,7 @@
           <t>江南市安良町八王子137</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 1.3km</t>
@@ -6237,17 +6209,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-23</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立古知野北保育園</t>
         </is>
@@ -6257,7 +6229,7 @@
           <t>江南市勝佐町田代137番地</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 3.3km</t>
@@ -6265,38 +6237,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-4　2-3-2　2-3-4　2-3-9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>合計　2社 / 5名 / 計7.0km</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -6344,51 +6316,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>教員 3　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C5</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="36" t="n">
+      <c r="A6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>ドコモショップ江南店</t>
         </is>
@@ -6398,7 +6370,7 @@
           <t>愛知県江南市木賀町定和163</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 2.4km</t>
@@ -6406,17 +6378,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-6　2-1-13</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立藤里保育園</t>
         </is>
@@ -6426,7 +6398,7 @@
           <t>江南市藤が丘7丁目1-16</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 3.4km</t>
@@ -6434,17 +6406,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-36</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="36" t="n">
+      <c r="A10" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>GARN（ガルン）　モゾワンダーシティ店</t>
         </is>
@@ -6454,7 +6426,7 @@
           <t>愛知県名古屋市西区二方町40番</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
 14.3km</t>
@@ -6462,38 +6434,38 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-4-1</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>合計　3社 / 4名 / 計32.1km</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -6544,51 +6516,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>教員 1　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C6</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>江南中央食品</t>
         </is>
@@ -6598,7 +6570,7 @@
           <t>江南市古知野町北屋敷242</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 2.0km</t>
@@ -6606,17 +6578,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-8</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>大口屋木賀工場</t>
         </is>
@@ -6626,7 +6598,7 @@
           <t>江南市木賀町定和244-1 その他</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 1.8km</t>
@@ -6634,38 +6606,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-29　1-5-37</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>合計　2社 / 3名 / 計6.1km</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -6713,51 +6685,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>教員 2　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C7</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>サンハウス食品株式会社</t>
         </is>
@@ -6767,7 +6739,7 @@
           <t>愛知県江南市高屋町西里７７番地</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 2.6km</t>
@@ -6775,17 +6747,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-16　1-5-19</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立草井保育園</t>
         </is>
@@ -6795,7 +6767,7 @@
           <t>江南市草井町若草57</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 1.9km</t>
@@ -6803,17 +6775,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-12　1-5-14</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>株式会社扶桑守口食品</t>
         </is>
@@ -6823,7 +6795,7 @@
           <t>愛知県丹羽郡扶桑町大字山那字屋敷地757</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
 2.1km</t>
@@ -6831,38 +6803,38 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-7　1-5-15</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>合計　3社 / 6名 / 計11.0km</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -6913,51 +6885,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>教員 3　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C8</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="36" t="n">
+      <c r="A6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>江南市立藤里保育園</t>
         </is>
@@ -6967,7 +6939,7 @@
           <t>江南市藤が丘7丁目1-16</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 3.6km</t>
@@ -6975,17 +6947,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 2-2-13</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>東名化学工業株式会社　小牧工場</t>
         </is>
@@ -6995,7 +6967,7 @@
           <t>小牧市大草檀之上5410</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 14.3km</t>
@@ -7003,38 +6975,38 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 2-1-15　2-4-20</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>合計　2社 / 3名 / 計28.7km</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="29" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -7082,51 +7054,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>教員 1　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C9</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>榮美容室本店</t>
         </is>
@@ -7136,7 +7108,7 @@
           <t>一宮市大江2-9-16</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 8.6km</t>
@@ -7144,38 +7116,38 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-27</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>合計　1社 / 1名 / 計17.3km</t>
         </is>
       </c>
-      <c r="D8" s="30" t="n"/>
+      <c r="D8" s="29" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="32" t="inlineStr"/>
+      <c r="A11" s="31" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="32" t="inlineStr"/>
+      <c r="A12" s="31" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr"/>
+      <c r="A13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="32" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -7220,51 +7192,51 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>教員 2　担当　　※このシートを持参してください</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>'全日程一覧'!C10</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>企業名　／　担当生徒</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>住　所　（訪問先）</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>江南中央食品</t>
         </is>
@@ -7274,7 +7246,7 @@
           <t>江南市古知野町北屋敷242</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
 2.0km</t>
@@ -7282,17 +7254,17 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-35</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>江南市立布袋西保育園</t>
         </is>
@@ -7302,7 +7274,7 @@
           <t>江南市木賀町定和３１</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>前より
 1.8km</t>
@@ -7310,17 +7282,17 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-4　1-5-22</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>ガレ・ドゥ・ワタナベ</t>
         </is>
@@ -7330,7 +7302,7 @@
           <t>江南市小折町八反畑8</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>前より
 1.5km</t>
@@ -7338,38 +7310,38 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>担当生徒: 1-5-11　1-5-13</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>合計　3社 / 5名 / 計7.7km</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr"/>
+      <c r="A15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="32" t="inlineStr"/>
+      <c r="A16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr"/>
+      <c r="A17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="32" t="inlineStr"/>
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/教員見回り配布用.xlsx
+++ b/教員見回り配布用.xlsx
@@ -1,44 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="全日程一覧" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="7-27月_教員1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="7-27月_教員2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="7-27月_教員3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="7-28火_教員1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="7-28火_教員2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7-28火_教員3" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="7-29水_教員1" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="7-29水_教員2" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="7-29水_教員3" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="7-29水_教員4" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="7-30木_教員1" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="7-30木_教員2" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="7-30木_教員3" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="7-30木_教員4" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="7-31金_教員1" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="7-31金_教員2" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="7-31金_教員3" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="7-31金_教員4" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="8-24月_教員1" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="8-24月_教員2" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="8-24月_教員3" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="8-25火_教員1" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="8-25火_教員2" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="8-25火_教員3" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="8-26水_教員1" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="8-26水_教員2" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="8-26水_教員3" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="8-26水_教員4" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="8-27木_教員1" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="8-27木_教員2" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="8-28金_教員1" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全日程一覧" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-27月_教員1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-27月_教員2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-27月_教員3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-28火_教員1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-28火_教員2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-28火_教員3" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-29水_教員1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-29水_教員2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-29水_教員3" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-29水_教員4" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-30木_教員1" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-30木_教員2" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-30木_教員3" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-30木_教員4" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-31金_教員1" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-31金_教員2" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-31金_教員3" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-31金_教員4" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-24月_教員1" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-24月_教員2" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-24月_教員3" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-25火_教員1" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-25火_教員2" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-25火_教員3" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-26水_教員1" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-26水_教員2" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-26水_教員3" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-26水_教員4" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-27木_教員1" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-27木_教員2" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-28金_教員1" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1367,22 +1367,22 @@
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>江南市立古知野東保育園 → グンゼ江南工場 → 江南市立宮田東保育園</t>
+          <t>グンゼ江南工場 → 江南市立宮田東保育園</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>江南市高屋町大師７２番地 ／ 愛知県江南市村久野町鳥附１番地 ／ 江南市宮田神明町栄174</t>
+          <t>愛知県江南市村久野町鳥附１番地 ／ 江南市宮田神明町栄174</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>2-4-22　1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25</t>
+          <t>1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>8.4km</t>
+          <t>8.3km</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>2-1-33　2-3-18　2-4-5　2-4-26　2-3-1　2-4-27</t>
+          <t>2-1-33　2-3-18　2-4-5　2-4-22　2-4-26　2-3-1　2-4-27</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -3209,7 +3209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3272,25 +3272,25 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>江南市立古知野東保育園</t>
+          <t>グンゼ江南工場</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>江南市高屋町大師７２番地</t>
+          <t>愛知県江南市村久野町鳥附１番地</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
           <t>学校から
-1.6km</t>
+2.8km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>担当生徒: 2-4-22</t>
+          <t>担当生徒: 1-5-24　2-1-29　2-1-32　2-3-12　2-3-15</t>
         </is>
       </c>
     </row>
@@ -3300,12 +3300,12 @@
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>グンゼ江南工場</t>
+          <t>江南市立宮田東保育園</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>愛知県江南市村久野町鳥附１番地</t>
+          <t>江南市宮田神明町栄174</t>
         </is>
       </c>
       <c r="D8" s="26" t="inlineStr">
@@ -3318,52 +3318,30 @@
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>担当生徒: 1-5-24　2-1-29　2-1-32　2-3-12　2-3-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>江南市立宮田東保育園</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>江南市宮田神明町栄174</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>前より
-1.3km</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="24" t="inlineStr">
-        <is>
           <t>担当生徒: 1-5-1　1-5-25</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>合計　3社 / 8名 / 計8.4km</t>
-        </is>
-      </c>
-      <c r="D12" s="29" t="n"/>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>合計　2社 / 7名 / 計8.3km</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="31" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="31" t="inlineStr"/>
@@ -3371,31 +3349,22 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="31" t="inlineStr"/>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="31" t="inlineStr"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="31" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="15">
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="A18:D18"/>
     <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
@@ -3887,7 +3856,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>担当生徒: 2-4-5　2-4-26</t>
+          <t>担当生徒: 2-4-5　2-4-22　2-4-26</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3891,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="28" t="inlineStr">
         <is>
-          <t>合計　3社 / 6名 / 計9.9km</t>
+          <t>合計　3社 / 7名 / 計9.9km</t>
         </is>
       </c>
       <c r="D12" s="29" t="n"/>
